--- a/XD8/Đoạn 3/4. K98 Base - XD8 đoạn 3.xlsx
+++ b/XD8/Đoạn 3/4. K98 Base - XD8 đoạn 3.xlsx
@@ -17,6 +17,9 @@
     <sheet name="Base B" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="KL Basa B" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rIdExt1"/>
+  </externalReferences>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">'Base A'!$A$1:$S$69</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Titles" vbProcedure="false">'Base A'!$21:$22</definedName>
@@ -1376,6 +1379,418 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="IN"/>
+      <sheetName val="Tuyến XD8"/>
+      <sheetName val="1. PL đường đen"/>
+      <sheetName val="2. Cao độ đào nền"/>
+      <sheetName val="2. KL đào nền"/>
+      <sheetName val="3. KTHH vải lọc"/>
+      <sheetName val="3. KL vải lọc"/>
+      <sheetName val="chạy VL"/>
+      <sheetName val="KL tưới nhựa"/>
+      <sheetName val="CĐ mặt đường"/>
+      <sheetName val="KL BTN"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="A3">
+            <v>57</v>
+          </cell>
+          <cell r="B3" t="str">
+            <v xml:space="preserve">Kiểm tra cao độ đường đen đoạn từ Km0+489,19 -:- Km0+609,11</v>
+          </cell>
+          <cell r="D3" t="str">
+            <v xml:space="preserve">ngày 12 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G3" t="str">
+            <v xml:space="preserve">57.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>58</v>
+          </cell>
+          <cell r="B4" t="str">
+            <v xml:space="preserve">Đào đất xử lý nền đường đoạn từ Km0+489,19 - Km0+609,11</v>
+          </cell>
+          <cell r="D4" t="str">
+            <v xml:space="preserve">ngày 13 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G4" t="str">
+            <v xml:space="preserve">58.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>59</v>
+          </cell>
+          <cell r="B5" t="str">
+            <v xml:space="preserve">Rải vải địa kỹ thuật đoạn từ Km0+489,19 - Km0+609,11</v>
+          </cell>
+          <cell r="D5" t="str">
+            <v xml:space="preserve">ngày 14 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G5" t="str">
+            <v xml:space="preserve">59.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>60</v>
+          </cell>
+          <cell r="B6" t="str">
+            <v xml:space="preserve">Đắp cát nền đường lớp 1 đoạn từ Km0+489,19 - Km0+609,11, độ chặt K&gt;=0,95</v>
+          </cell>
+          <cell r="D6" t="str">
+            <v xml:space="preserve">ngày 14 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G6" t="str">
+            <v xml:space="preserve">60.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>61</v>
+          </cell>
+          <cell r="B7" t="str">
+            <v xml:space="preserve">Đắp cát nền đường lớp 2 đoạn từ Km0+489,19 - Km0+609,11, độ chặt K&gt;=0,95</v>
+          </cell>
+          <cell r="D7" t="str">
+            <v xml:space="preserve">ngày 15 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G7" t="str">
+            <v xml:space="preserve">61.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>62</v>
+          </cell>
+          <cell r="B8" t="str">
+            <v xml:space="preserve">Đắp cát nền đường lớp 3 đoạn từ Km0+489,19 - Km0+609,11, độ chặt K&gt;=0,95</v>
+          </cell>
+          <cell r="D8" t="str">
+            <v xml:space="preserve">ngày 15 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G8" t="str">
+            <v xml:space="preserve">62.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>63</v>
+          </cell>
+          <cell r="B9" t="str">
+            <v xml:space="preserve">Đắp cát nền đường lớp 4 đoạn từ Km0+489,19 - Km0+609,11, độ chặt K&gt;=0,95</v>
+          </cell>
+          <cell r="D9" t="str">
+            <v xml:space="preserve">ngày 16 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G9" t="str">
+            <v xml:space="preserve">63.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>64</v>
+          </cell>
+          <cell r="B10" t="str">
+            <v xml:space="preserve">Đắp đất nền đường lớp 1 đoạn từ Km0+489,19 - Km0+609,11, độ chặt K&gt;=0,95</v>
+          </cell>
+          <cell r="D10" t="str">
+            <v xml:space="preserve">ngày 16 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G10" t="str">
+            <v xml:space="preserve">64.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>65</v>
+          </cell>
+          <cell r="B11" t="str">
+            <v xml:space="preserve">Đắp đất nền đường lớp 2 đoạn từ Km0+489,19 - Km0+609,11, độ chặt K&gt;=0,95</v>
+          </cell>
+          <cell r="D11" t="str">
+            <v xml:space="preserve">ngày 17 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G11" t="str">
+            <v xml:space="preserve">65.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>66</v>
+          </cell>
+          <cell r="B12" t="str">
+            <v xml:space="preserve">Đắp đất nền đường lớp 3 đoạn từ Km0+489,19 - Km0+609,11, độ chặt K&gt;=0,95</v>
+          </cell>
+          <cell r="D12" t="str">
+            <v xml:space="preserve">ngày 17 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G12" t="str">
+            <v xml:space="preserve">66.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>67</v>
+          </cell>
+          <cell r="B13" t="str">
+            <v xml:space="preserve">Đắp đất nền đường lớp 4 đoạn từ Km0+489,19 - Km0+609,11, độ chặt K&gt;=0,95</v>
+          </cell>
+          <cell r="D13" t="str">
+            <v xml:space="preserve">ngày 18 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G13" t="str">
+            <v xml:space="preserve">67.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>68</v>
+          </cell>
+          <cell r="B14" t="str">
+            <v xml:space="preserve">Đắp đất nền đường lớp 5 đoạn từ Km0+489,19 - Km0+609,11, độ chặt K&gt;=0,95</v>
+          </cell>
+          <cell r="D14" t="str">
+            <v xml:space="preserve">ngày 18 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G14" t="str">
+            <v xml:space="preserve">68.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>69</v>
+          </cell>
+          <cell r="B15" t="str">
+            <v xml:space="preserve">Đắp đất nền đường lớp 6 đoạn từ Km0+489,19 - Km0+609,11, độ chặt K&gt;=0,95</v>
+          </cell>
+          <cell r="D15" t="str">
+            <v xml:space="preserve">ngày 19 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G15" t="str">
+            <v xml:space="preserve">69.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>70</v>
+          </cell>
+          <cell r="B16" t="str">
+            <v xml:space="preserve">Đắp đất nền đường lớp 7 đoạn từ Km0+489,19 - Km0+609,11, độ chặt K&gt;=0,95</v>
+          </cell>
+          <cell r="D16" t="str">
+            <v xml:space="preserve">ngày 19 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G16" t="str">
+            <v xml:space="preserve">70.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>71</v>
+          </cell>
+          <cell r="B17" t="str">
+            <v xml:space="preserve">Đắp đất nền đường lớp 8 đoạn từ Km0+489,19 - Km0+609,11, độ chặt K&gt;=0,95</v>
+          </cell>
+          <cell r="D17" t="str">
+            <v xml:space="preserve">ngày 20 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G17" t="str">
+            <v xml:space="preserve">71.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>72</v>
+          </cell>
+          <cell r="B18" t="str">
+            <v xml:space="preserve">Đắp đất nền đường lớp 1, độ chặt K&gt;=0,98 đoạn từ Km0+489,19 - Km0+609,11</v>
+          </cell>
+          <cell r="D18" t="str">
+            <v xml:space="preserve">ngày 21 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G18" t="str">
+            <v xml:space="preserve">72.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>73</v>
+          </cell>
+          <cell r="B19" t="str">
+            <v xml:space="preserve">Đắp đất lề đường lớp 1, độ chặt K&gt;=0,95 đoạn từ Km0+489,19 - Km0+609,11</v>
+          </cell>
+          <cell r="D19" t="str">
+            <v xml:space="preserve">ngày 21 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G19" t="str">
+            <v xml:space="preserve">73.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>74</v>
+          </cell>
+          <cell r="B20" t="str">
+            <v xml:space="preserve">Đắp đất nền đường lớp 2, độ chặt K&gt;=0,98 đoạn từ Km0+489,19 - Km0+609,11</v>
+          </cell>
+          <cell r="D20" t="str">
+            <v xml:space="preserve">ngày 22 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G20" t="str">
+            <v xml:space="preserve">74.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>75</v>
+          </cell>
+          <cell r="B21" t="str">
+            <v xml:space="preserve">Đắp đất lề đường lớp 2, độ chặt K&gt;=0,95 đoạn từ Km0+489,19 - Km0+609,11</v>
+          </cell>
+          <cell r="D21" t="str">
+            <v xml:space="preserve">ngày 22 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G21" t="str">
+            <v xml:space="preserve">75.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>76</v>
+          </cell>
+          <cell r="B22" t="str">
+            <v xml:space="preserve">Đắp cấp phối đá dăm loại 2 đoạn từ Km0+489,19 - Km0+609,11</v>
+          </cell>
+          <cell r="D22" t="str">
+            <v xml:space="preserve">ngày 23 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G22" t="str">
+            <v xml:space="preserve">76.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>77</v>
+          </cell>
+          <cell r="B23" t="str">
+            <v xml:space="preserve">Đắp đất lề đường lớp 3, độ chặt K&gt;=0,95 đoạn từ Km0+489,19 - Km0+609,11</v>
+          </cell>
+          <cell r="D23" t="str">
+            <v xml:space="preserve">ngày 23 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G23" t="str">
+            <v xml:space="preserve">77.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>78</v>
+          </cell>
+          <cell r="B24" t="str">
+            <v xml:space="preserve">Đắp đất lề đường lớp 4, độ chặt K&gt;=0,95 đoạn từ Km0+489,19 - Km0+609,11</v>
+          </cell>
+          <cell r="D24" t="str">
+            <v xml:space="preserve">ngày 24 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G24" t="str">
+            <v xml:space="preserve">78.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>79</v>
+          </cell>
+          <cell r="B25" t="str">
+            <v xml:space="preserve">Đắp cấp phối đá dăm loại 1 đoạn từ Km0+489,19 - Km0+609,11</v>
+          </cell>
+          <cell r="D25" t="str">
+            <v xml:space="preserve">ngày 24 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G25" t="str">
+            <v xml:space="preserve">79.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>80</v>
+          </cell>
+          <cell r="B26" t="str">
+            <v xml:space="preserve">Vệ sinh, thổi bụi mặt đường </v>
+          </cell>
+          <cell r="D26" t="str">
+            <v xml:space="preserve">ngày 26 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G26" t="str">
+            <v xml:space="preserve">80.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>81</v>
+          </cell>
+          <cell r="B27" t="str">
+            <v xml:space="preserve">Tưới lớp thấm bám mặt đường, nhựa MC70, lượng nhựa 1kg/m2</v>
+          </cell>
+          <cell r="D27" t="str">
+            <v xml:space="preserve">ngày 28 tháng 09 năm 2026</v>
+          </cell>
+          <cell r="G27" t="str">
+            <v xml:space="preserve">81.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>82</v>
+          </cell>
+          <cell r="B28" t="str">
+            <v xml:space="preserve">Rải thảm mặt đường bê tông nhựa C16 - Chiều dày mặt đường đã lèn ép 6cm</v>
+          </cell>
+          <cell r="D28" t="str">
+            <v xml:space="preserve">ngày 01 tháng 10 năm 2026</v>
+          </cell>
+          <cell r="G28" t="str">
+            <v xml:space="preserve">82.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>83</v>
+          </cell>
+          <cell r="B29" t="str">
+            <v xml:space="preserve">Bê tông nhựa C16 - Chiều dày mặt đường đã lèn ép 6cm</v>
+          </cell>
+          <cell r="D29" t="str">
+            <v xml:space="preserve">ngày 03 tháng 10 năm 2026</v>
+          </cell>
+          <cell r="G29" t="str">
+            <v xml:space="preserve">83.NĐXD8/CVXD </v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
@@ -1599,8 +2014,9 @@
       <c r="W1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>1</v>
+      <c r="A2" s="4" t="str">
+        <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,4,0)</f>
+        <v xml:space="preserve">Kèm theo BBNT số: 72.NĐXD8/CVXD ngày 21 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -1623,6 +2039,9 @@
       <c r="U2" s="5"/>
       <c r="V2" s="5"/>
       <c r="W2" s="5"/>
+      <c r="AZ2">
+        <v>72</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
@@ -1735,8 +2154,9 @@
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="F7" s="6"/>
-      <c r="G7" s="6" t="s">
-        <v>7</v>
+      <c r="G7" s="6" t="str">
+        <f>VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$B$60,2,0)</f>
+        <v xml:space="preserve">Đắp đất nền đường lớp 1, độ chặt K&gt;=0,98 đoạn từ Km0+489,19 - Km0+609,11</v>
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
@@ -3621,8 +4041,9 @@
       <c r="AB1" s="26"/>
     </row>
     <row r="2" s="27" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="28" t="s">
-        <v>1</v>
+      <c r="A2" s="28" t="str">
+        <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,4,0)</f>
+        <v xml:space="preserve">Kèm theo BBNT số: 72.NĐXD8/CVXD ngày 21 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -3651,6 +4072,9 @@
       <c r="Z2" s="28"/>
       <c r="AA2" s="28"/>
       <c r="AB2" s="28"/>
+      <c r="AZ2">
+        <v>72</v>
+      </c>
     </row>
     <row r="3" s="31" customFormat="true" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
@@ -4605,8 +5029,9 @@
         <v>6</v>
       </c>
       <c r="B7" s="33"/>
-      <c r="D7" s="34" t="s">
-        <v>7</v>
+      <c r="D7" s="34" t="str">
+        <f>VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$B$60,2,0)</f>
+        <v xml:space="preserve">Đắp đất nền đường lớp 1, độ chặt K&gt;=0,98 đoạn từ Km0+489,19 - Km0+609,11</v>
       </c>
       <c r="E7" s="34"/>
       <c r="F7" s="34"/>
@@ -9330,8 +9755,9 @@
       <c r="W1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>47</v>
+      <c r="A2" s="4" t="str">
+        <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,4,0)</f>
+        <v xml:space="preserve">Kèm theo BBNT số: 74.NĐXD8/CVXD ngày 22 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -9354,6 +9780,9 @@
       <c r="U2" s="5"/>
       <c r="V2" s="5"/>
       <c r="W2" s="5"/>
+      <c r="AZ2">
+        <v>74</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
@@ -9466,8 +9895,9 @@
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="F7" s="6"/>
-      <c r="G7" s="6" t="s">
-        <v>48</v>
+      <c r="G7" s="6" t="str">
+        <f>VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$B$60,2,0)</f>
+        <v xml:space="preserve">Đắp đất nền đường lớp 2, độ chặt K&gt;=0,98 đoạn từ Km0+489,19 - Km0+609,11</v>
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
@@ -11431,8 +11861,9 @@
       <c r="AB1" s="26"/>
     </row>
     <row r="2" s="27" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="28" t="s">
-        <v>47</v>
+      <c r="A2" s="28" t="str">
+        <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,4,0)</f>
+        <v xml:space="preserve">Kèm theo BBNT số: 74.NĐXD8/CVXD ngày 22 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -11461,6 +11892,9 @@
       <c r="Z2" s="28"/>
       <c r="AA2" s="28"/>
       <c r="AB2" s="28"/>
+      <c r="AZ2">
+        <v>74</v>
+      </c>
     </row>
     <row r="3" s="31" customFormat="true" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
@@ -12415,8 +12849,9 @@
         <v>6</v>
       </c>
       <c r="B7" s="33"/>
-      <c r="D7" s="34" t="s">
-        <v>48</v>
+      <c r="D7" s="34" t="str">
+        <f>VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$B$60,2,0)</f>
+        <v xml:space="preserve">Đắp đất nền đường lớp 2, độ chặt K&gt;=0,98 đoạn từ Km0+489,19 - Km0+609,11</v>
       </c>
       <c r="E7" s="34"/>
       <c r="F7" s="34"/>
@@ -17064,8 +17499,9 @@
       <c r="W1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>49</v>
+      <c r="A2" s="4" t="str">
+        <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,4,0)</f>
+        <v xml:space="preserve">Kèm theo BBNT số: 76.NĐXD8/CVXD ngày 23 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -17088,6 +17524,9 @@
       <c r="U2" s="5"/>
       <c r="V2" s="5"/>
       <c r="W2" s="5"/>
+      <c r="AZ2">
+        <v>76</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
@@ -17200,8 +17639,9 @@
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="F7" s="6"/>
-      <c r="G7" s="6" t="s">
-        <v>50</v>
+      <c r="G7" s="6" t="str">
+        <f>VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$B$60,2,0)</f>
+        <v xml:space="preserve">Đắp cấp phối đá dăm loại 2 đoạn từ Km0+489,19 - Km0+609,11</v>
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
@@ -19165,8 +19605,9 @@
       <c r="AB1" s="26"/>
     </row>
     <row r="2" s="27" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="28" t="s">
-        <v>49</v>
+      <c r="A2" s="28" t="str">
+        <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,4,0)</f>
+        <v xml:space="preserve">Kèm theo BBNT số: 76.NĐXD8/CVXD ngày 23 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -19195,6 +19636,9 @@
       <c r="Z2" s="28"/>
       <c r="AA2" s="28"/>
       <c r="AB2" s="28"/>
+      <c r="AZ2">
+        <v>76</v>
+      </c>
     </row>
     <row r="3" s="31" customFormat="true" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
@@ -20149,8 +20593,9 @@
         <v>6</v>
       </c>
       <c r="B7" s="33"/>
-      <c r="D7" s="34" t="s">
-        <v>50</v>
+      <c r="D7" s="34" t="str">
+        <f>VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$B$60,2,0)</f>
+        <v xml:space="preserve">Đắp cấp phối đá dăm loại 2 đoạn từ Km0+489,19 - Km0+609,11</v>
       </c>
       <c r="E7" s="34"/>
       <c r="F7" s="34"/>
@@ -24798,8 +25243,9 @@
       <c r="W1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>51</v>
+      <c r="A2" s="4" t="str">
+        <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,4,0)</f>
+        <v xml:space="preserve">Kèm theo BBNT số: 79.NĐXD8/CVXD ngày 24 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -24822,6 +25268,9 @@
       <c r="U2" s="5"/>
       <c r="V2" s="5"/>
       <c r="W2" s="5"/>
+      <c r="AZ2">
+        <v>79</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
@@ -24934,8 +25383,9 @@
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="F7" s="6"/>
-      <c r="G7" s="6" t="s">
-        <v>52</v>
+      <c r="G7" s="6" t="str">
+        <f>VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$B$60,2,0)</f>
+        <v xml:space="preserve">Đắp cấp phối đá dăm loại 1 đoạn từ Km0+489,19 - Km0+609,11</v>
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
@@ -26899,8 +27349,9 @@
       <c r="AB1" s="26"/>
     </row>
     <row r="2" s="27" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="28" t="s">
-        <v>51</v>
+      <c r="A2" s="28" t="str">
+        <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$G$60,4,0)</f>
+        <v xml:space="preserve">Kèm theo BBNT số: 79.NĐXD8/CVXD ngày 24 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -26929,6 +27380,9 @@
       <c r="Z2" s="28"/>
       <c r="AA2" s="28"/>
       <c r="AB2" s="28"/>
+      <c r="AZ2">
+        <v>79</v>
+      </c>
     </row>
     <row r="3" s="31" customFormat="true" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
@@ -27883,8 +28337,9 @@
         <v>6</v>
       </c>
       <c r="B7" s="33"/>
-      <c r="D7" s="34" t="s">
-        <v>52</v>
+      <c r="D7" s="34" t="str">
+        <f>VLOOKUP(AZ2,'[1]Tuyến XD8'!$A$2:$B$60,2,0)</f>
+        <v xml:space="preserve">Đắp cấp phối đá dăm loại 1 đoạn từ Km0+489,19 - Km0+609,11</v>
       </c>
       <c r="E7" s="34"/>
       <c r="F7" s="34"/>

--- a/XD8/Đoạn 3/4. K98 Base - XD8 đoạn 3.xlsx
+++ b/XD8/Đoạn 3/4. K98 Base - XD8 đoạn 3.xlsx
@@ -160,7 +160,7 @@
     <t xml:space="preserve">Nguyễn Xuân Hưng</t>
   </si>
   <si>
-    <t xml:space="preserve">Trần Mạnh Tùng</t>
+    <t xml:space="preserve">Lê Quốc Huy</t>
   </si>
   <si>
     <t xml:space="preserve">PHỤ LỤC KHỐI LƯỢNG </t>
